--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="840" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF8640F2-3769-4212-8C6A-297433652376}"/>
+  <xr:revisionPtr revIDLastSave="848" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237262FA-B1A5-49FB-BABA-07CC0640DCF3}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1 Y Tabl Cyfnodol ar Atom" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -167,7 +167,7 @@
     <t>2.8.1</t>
   </si>
   <si>
-    <t>Beth yw'rnifer mwyaf o electronau sy'n gallu ffitio yn y plisgyn 1af?</t>
+    <t>Beth yw'r nifer mwyaf o electronau sy'n gallu ffitio yn y plisgyn 1af?</t>
   </si>
   <si>
     <t>Beth yw'r nifer mwyaf o electronau sy'n gallu ffitio yn yr ail blisgyn?</t>
@@ -179,15 +179,9 @@
     <t>Eglurwch pa grŵp mae'r elfen sydd ag adeiledd electronig&lt;b&gt;&lt;b&gt;&lt;b&gt;2.8.5</t>
   </si>
   <si>
-    <t>Grŵp 5&lt;b&gt;oherwydd bod 3 electron yn y plisgyn ALLANOL</t>
-  </si>
-  <si>
     <t>Eglurwch pa GYFNOD mae'r elfen sydd ag adeiledd electronig&lt;b&gt;&lt;b&gt;&lt;b&gt;2.8.3</t>
   </si>
   <si>
-    <t>Cyfnod 3&lt;b&gt; oherwydd bod 3 plisgyn o electronau</t>
-  </si>
-  <si>
     <t>Beth yw elfen?</t>
   </si>
   <si>
@@ -218,6 +212,9 @@
     <t>carbon a hydrogen</t>
   </si>
   <si>
+    <t>Cyfansoddion.png</t>
+  </si>
+  <si>
     <t>Rhowch gyfanswm nifer yr atomau sydd mewn moleciwl o nitrogen deuocsid</t>
   </si>
   <si>
@@ -233,6 +230,9 @@
     <t>B</t>
   </si>
   <si>
+    <t>Moleciwlau.png</t>
+  </si>
+  <si>
     <t>Mae asid sylffwrig yn cynnwys dau atom o hydrogen, un atom o sylffwr a pedwar atom o ocsigen. Beth yw ei fformiwla?</t>
   </si>
   <si>
@@ -267,13 +267,19 @@
   </si>
   <si>
     <t>lithiwm ocsid</t>
+  </si>
+  <si>
+    <t>Grŵp 5&lt;br&gt;oherwydd bod 3 electron yn y plisgyn ALLANOL</t>
+  </si>
+  <si>
+    <t>Cyfnod 3&lt;br&gt; oherwydd bod 3 plisgyn o electronau</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -349,6 +355,12 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -377,12 +389,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -392,8 +403,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -417,6 +426,11 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,483 +652,498 @@
   <dimension ref="A1:F42"/>
   <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="47" style="12"/>
-    <col min="2" max="2" width="47" style="11"/>
-    <col min="3" max="3" width="33.5703125" style="8" customWidth="1"/>
-    <col min="4" max="16384" width="47" style="8"/>
+    <col min="1" max="1" width="47" style="9"/>
+    <col min="2" max="2" width="47" style="22"/>
+    <col min="3" max="3" width="33.5703125" style="7" customWidth="1"/>
+    <col min="4" max="16384" width="47" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="9" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="9" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="18">
         <v>1</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="18">
         <v>1</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="18">
         <v>11</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="18">
         <v>23</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="18">
         <v>11</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="18">
         <v>11</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="18">
         <v>2</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="18">
         <v>8</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="18">
         <v>8</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
+      <c r="B27" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B28" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A29" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B29" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B30" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B31" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A31" s="5" t="s">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A32" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B32" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A32" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="11" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A33" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
+      <c r="B33" s="18">
+        <v>3</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B34" s="22">
+        <v>8</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A35" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="22">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A35" s="12" t="s">
+      <c r="C35" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A36" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A36" s="12" t="s">
+      <c r="B36" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="C36" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A37" s="12" t="s">
+    <row r="37" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A37" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="22" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A38" s="12" t="s">
+    <row r="38" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A38" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A39" s="12" t="s">
+    <row r="39" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A39" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="22" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A40" s="12" t="s">
+    <row r="40" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A40" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="22" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A41" s="12" t="s">
+    <row r="41" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A41" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A42" s="12" t="s">
+    <row r="42" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A42" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="22" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1129,16 +1158,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30.75" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1153,28 +1182,28 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="49.42578125" style="15" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="4" width="49.42578125" style="12" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1">
-      <c r="D2" s="16"/>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="25.5" customHeight="1"/>
     <row r="4" spans="1:6" ht="25.5" customHeight="1"/>
@@ -1216,22 +1245,22 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="15" customWidth="1"/>
-    <col min="2" max="4" width="40.7109375" style="15" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="57.42578125" style="12" customWidth="1"/>
+    <col min="2" max="4" width="40.7109375" style="12" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="29.25" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1273,25 +1302,25 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="6" width="64.140625" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="14"/>
+    <col min="1" max="6" width="64.140625" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.5" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="3" spans="1:6" ht="27.75" customHeight="1"/>
@@ -1300,13 +1329,13 @@
     <row r="6" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="7" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="8" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A8" s="15"/>
+      <c r="A8" s="12"/>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A9" s="15"/>
+      <c r="A9" s="12"/>
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A10" s="15"/>
+      <c r="A10" s="12"/>
     </row>
     <row r="11" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="12" spans="1:6" ht="27.75" customHeight="1"/>
@@ -1314,21 +1343,21 @@
     <row r="14" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="15" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="16" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="17" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="18" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="19" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="20" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="21" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="22" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="23" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="24" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="25" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="26" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="27" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="28" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="29" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="30" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="31" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="17" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="18" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="19" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="20" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="21" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="22" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="23" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="24" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="25" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="26" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="27" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="28" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="29" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="30" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="31" s="11" customFormat="1" ht="27.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1339,23 +1368,23 @@
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="68.140625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="52.140625" style="18" customWidth="1"/>
-    <col min="3" max="4" width="42.140625" style="18" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="18"/>
+    <col min="1" max="1" width="68.140625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" style="15" customWidth="1"/>
+    <col min="3" max="4" width="42.140625" style="15" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="31.5" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1387,35 +1416,35 @@
     <row r="27" spans="2:2" ht="31.5" customHeight="1"/>
     <row r="28" spans="2:2" ht="31.5" customHeight="1"/>
     <row r="29" spans="2:2" ht="31.5" customHeight="1">
-      <c r="B29" s="19"/>
+      <c r="B29" s="16"/>
     </row>
     <row r="30" spans="2:2" ht="31.5" customHeight="1"/>
     <row r="31" spans="2:2" ht="31.5" customHeight="1"/>
     <row r="32" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="33" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="34" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="35" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="36" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="37" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="38" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="39" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="40" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="41" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="42" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="43" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="44" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="45" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="46" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="47" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="48" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="49" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="50" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="51" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="52" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="53" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="54" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="55" s="18" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="56" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="33" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="34" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="35" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="36" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="37" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="38" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="39" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="40" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="41" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="42" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="43" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="44" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="45" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="46" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="47" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="48" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="49" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="50" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="51" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="52" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="53" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="54" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="55" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="56" s="15" customFormat="1" ht="31.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1430,23 +1459,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="24.75" customHeight="1"/>
     <row r="3" spans="1:9" ht="24.75" customHeight="1"/>

--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="848" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237262FA-B1A5-49FB-BABA-07CC0640DCF3}"/>
+  <xr:revisionPtr revIDLastSave="855" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03E23828-4B53-4D22-9352-748CD18C90C9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="80">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Beth yw mas niwtron?</t>
   </si>
   <si>
-    <t>Pa rif yw'r RHIF ATOMIG? &lt;br&gt;&lt;br&gt;$\ce{^23_11Na}$</t>
-  </si>
-  <si>
     <t>Pa rif yw'r RHIF MAS? &lt;br&gt;&lt;br&gt;$\ce{^23_11Na}$</t>
   </si>
   <si>
@@ -273,13 +270,25 @@
   </si>
   <si>
     <t>Cyfnod 3&lt;br&gt; oherwydd bod 3 plisgyn o electronau</t>
+  </si>
+  <si>
+    <t>Pa rif yw'r RHIF ATOMIG? &lt;br&gt;&lt;br&gt; $\ce{^23_11Na}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 23</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -304,56 +313,64 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -650,7 +667,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" style="9"/>
     <col min="2" max="2" width="47" style="22"/>
@@ -658,7 +675,7 @@
     <col min="4" max="16384" width="47" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,7 +691,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -686,7 +703,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -700,7 +717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -714,7 +731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
@@ -726,7 +743,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -738,7 +755,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -750,7 +767,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -762,7 +779,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
@@ -774,7 +791,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
@@ -786,7 +803,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -798,7 +815,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -810,7 +827,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -822,19 +839,19 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="18">
-        <v>1</v>
+      <c r="B14" s="18" t="s">
+        <v>77</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
@@ -846,93 +863,93 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="18">
-        <v>1</v>
+      <c r="B16" s="18" t="s">
+        <v>77</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="18">
-        <v>11</v>
+        <v>76</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="18">
-        <v>23</v>
+        <v>33</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="18">
-        <v>11</v>
+        <v>34</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="18">
-        <v>11</v>
+        <v>35</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>37</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>38</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" s="18">
         <v>2</v>
@@ -942,9 +959,9 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" s="18">
         <v>8</v>
@@ -954,9 +971,9 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="18">
         <v>8</v>
@@ -966,179 +983,179 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="18" t="s">
         <v>46</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>47</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>48</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>49</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="18" t="s">
         <v>50</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>51</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="18" t="s">
         <v>52</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>53</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="C32" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="7" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="B33" s="18">
         <v>3</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B34" s="22">
         <v>8</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B35" s="22">
         <v>3</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="C36" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="7" t="s">
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A37" s="9" t="s">
+      <c r="B37" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="22" t="s">
+    </row>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A38" s="9" t="s">
+      <c r="B38" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="22" t="s">
+    </row>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A39" s="9" t="s">
+      <c r="B39" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="22" t="s">
+    </row>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A40" s="9" t="s">
+      <c r="B40" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="B40" s="22" t="s">
+    </row>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A41" s="9" t="s">
+      <c r="B41" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="22" t="s">
+    </row>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A42" s="9" t="s">
+      <c r="B42" s="22" t="s">
         <v>73</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1150,14 +1167,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57DDB98-DED6-44B3-9212-7621DBC6158B}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
     <col min="3" max="4" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75" customHeight="1">
+    <row r="1" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" customFormat="1"/>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1180,13 +1197,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608DC02D-A3BC-4E94-A0C9-91816C3DAF43}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="49.42578125" style="12" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.5" customHeight="1">
+    <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1202,39 +1219,39 @@
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
-    <row r="2" spans="1:6" ht="25.5" customHeight="1">
+    <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="13"/>
     </row>
-    <row r="3" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="4" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="5" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="6" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="7" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="8" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="9" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="10" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="11" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="12" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="13" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="14" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="15" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="16" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="17" ht="25.5" customHeight="1"/>
-    <row r="18" ht="25.5" customHeight="1"/>
-    <row r="19" ht="25.5" customHeight="1"/>
-    <row r="20" ht="25.5" customHeight="1"/>
-    <row r="21" ht="25.5" customHeight="1"/>
-    <row r="22" ht="25.5" customHeight="1"/>
-    <row r="23" ht="25.5" customHeight="1"/>
-    <row r="24" ht="25.5" customHeight="1"/>
-    <row r="25" ht="25.5" customHeight="1"/>
-    <row r="26" ht="25.5" customHeight="1"/>
-    <row r="27" ht="25.5" customHeight="1"/>
-    <row r="28" ht="25.5" customHeight="1"/>
-    <row r="29" ht="25.5" customHeight="1"/>
-    <row r="30" ht="25.5" customHeight="1"/>
-    <row r="31" ht="25.5" customHeight="1"/>
-    <row r="32" ht="25.5" customHeight="1"/>
+    <row r="3" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1243,14 +1260,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7390D3-77B8-417A-BF28-251115C36B48}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="57.42578125" style="12" customWidth="1"/>
     <col min="2" max="4" width="40.7109375" style="12" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29.25" customHeight="1">
+    <row r="1" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1264,34 +1281,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="3" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="4" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="5" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="6" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="7" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="8" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="9" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="10" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="11" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="12" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="13" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="14" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="15" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="16" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="17" ht="29.25" customHeight="1"/>
-    <row r="18" ht="29.25" customHeight="1"/>
-    <row r="19" ht="29.25" customHeight="1"/>
-    <row r="20" ht="29.25" customHeight="1"/>
-    <row r="21" ht="29.25" customHeight="1"/>
-    <row r="22" ht="29.25" customHeight="1"/>
-    <row r="23" ht="29.25" customHeight="1"/>
-    <row r="24" ht="29.25" customHeight="1"/>
-    <row r="25" ht="29.25" customHeight="1"/>
-    <row r="26" ht="29.25" customHeight="1"/>
-    <row r="27" ht="29.25" customHeight="1"/>
-    <row r="28" ht="29.25" customHeight="1"/>
-    <row r="29" ht="29.25" customHeight="1"/>
+    <row r="2" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1300,13 +1317,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C1C183-043C-4181-ABFC-6CC837CF0487}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="64.140625" style="11" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.5" customHeight="1">
+    <row r="1" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1322,42 +1339,42 @@
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
-    <row r="2" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="3" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="4" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="5" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="6" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="7" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="8" spans="1:6" ht="27.75" customHeight="1">
+    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
     </row>
-    <row r="9" spans="1:6" ht="27.75" customHeight="1">
+    <row r="9" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
     </row>
-    <row r="10" spans="1:6" ht="27.75" customHeight="1">
+    <row r="10" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
     </row>
-    <row r="11" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="12" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="13" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="14" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="15" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="16" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="17" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="18" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="19" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="20" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="21" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="22" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="23" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="24" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="25" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="26" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="27" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="28" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="29" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="30" s="11" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="31" s="11" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="11" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1366,7 +1383,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D33F75-CDBA-43E0-9D68-0D698FDC504D}">
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="68.140625" style="15" customWidth="1"/>
     <col min="2" max="2" width="52.140625" style="15" customWidth="1"/>
@@ -1374,7 +1391,7 @@
     <col min="5" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" customHeight="1">
+    <row r="1" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1388,63 +1405,63 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="3" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="4" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="5" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="6" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="7" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="8" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="9" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="10" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="11" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="12" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="13" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="14" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="15" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="16" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="17" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="18" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="19" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="20" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="21" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="22" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="23" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="24" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="25" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="26" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="27" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="28" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="29" spans="2:2" ht="31.5" customHeight="1">
+    <row r="2" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="16"/>
     </row>
-    <row r="30" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="31" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="32" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="33" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="34" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="35" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="36" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="37" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="38" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="39" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="40" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="41" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="42" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="43" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="44" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="45" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="46" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="47" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="48" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="49" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="50" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="51" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="52" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="53" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="54" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="55" s="15" customFormat="1" ht="31.5" customHeight="1"/>
-    <row r="56" s="15" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="30" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1453,12 +1470,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A950653-FD65-41B9-B4CE-86A2AB4CA7C0}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24.75" customHeight="1">
+    <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1477,42 +1494,42 @@
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="3" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="4" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="5" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="6" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="7" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="8" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="9" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="10" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="11" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="12" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="13" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="14" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="15" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="16" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="17" ht="24.75" customHeight="1"/>
-    <row r="18" ht="24.75" customHeight="1"/>
-    <row r="19" ht="24.75" customHeight="1"/>
-    <row r="20" ht="24.75" customHeight="1"/>
-    <row r="21" ht="24.75" customHeight="1"/>
-    <row r="22" ht="24.75" customHeight="1"/>
-    <row r="23" ht="24.75" customHeight="1"/>
-    <row r="24" ht="24.75" customHeight="1"/>
-    <row r="25" ht="24.75" customHeight="1"/>
-    <row r="26" ht="24.75" customHeight="1"/>
-    <row r="27" ht="24.75" customHeight="1"/>
-    <row r="28" ht="24.75" customHeight="1"/>
-    <row r="29" ht="24.75" customHeight="1"/>
-    <row r="30" ht="24.75" customHeight="1"/>
-    <row r="31" ht="24.75" customHeight="1"/>
-    <row r="32" ht="24.75" customHeight="1"/>
-    <row r="33" ht="24.75" customHeight="1"/>
-    <row r="34" ht="24.75" customHeight="1"/>
-    <row r="35" ht="24.75" customHeight="1"/>
-    <row r="36" ht="24.75" customHeight="1"/>
-    <row r="37" ht="24.75" customHeight="1"/>
+    <row r="2" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="855" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03E23828-4B53-4D22-9352-748CD18C90C9}"/>
+  <xr:revisionPtr revIDLastSave="869" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD1FC67E-6A2E-47C1-8B53-6AE35B4EE244}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="83">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -173,12 +173,6 @@
     <t>Beth yw'r nifer mwyaf o electronau sy'n gallu ffitio yn y trydydd plisgyn?</t>
   </si>
   <si>
-    <t>Eglurwch pa grŵp mae'r elfen sydd ag adeiledd electronig&lt;b&gt;&lt;b&gt;&lt;b&gt;2.8.5</t>
-  </si>
-  <si>
-    <t>Eglurwch pa GYFNOD mae'r elfen sydd ag adeiledd electronig&lt;b&gt;&lt;b&gt;&lt;b&gt;2.8.3</t>
-  </si>
-  <si>
     <t>Beth yw elfen?</t>
   </si>
   <si>
@@ -275,13 +269,28 @@
     <t>Pa rif yw'r RHIF ATOMIG? &lt;br&gt;&lt;br&gt; $\ce{^23_11Na}$</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 23</t>
+    <t>Eglurwch pa grŵp mae'r elfen sydd ag adeiledd electronig&lt;br&gt;&lt;br&gt;&lt;br&gt;2.8.5</t>
+  </si>
+  <si>
+    <t>Eglurwch pa GYFNOD mae'r elfen sydd ag adeiledd electronig&lt;br&gt;&lt;br&gt;&lt;br&gt;2.8.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "1"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "11"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "23"</t>
+  </si>
+  <si>
+    <t>"2"</t>
+  </si>
+  <si>
+    <t>"3"</t>
+  </si>
+  <si>
+    <t>"8"</t>
   </si>
 </sst>
 </file>
@@ -463,6 +472,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -877,7 +890,7 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>78</v>
@@ -951,8 +964,8 @@
       <c r="A23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="18">
-        <v>2</v>
+      <c r="B23" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -963,8 +976,8 @@
       <c r="A24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="18">
-        <v>8</v>
+      <c r="B24" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -975,8 +988,8 @@
       <c r="A25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="18">
-        <v>8</v>
+      <c r="B25" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -985,10 +998,10 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -997,10 +1010,10 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -1009,10 +1022,10 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -1021,10 +1034,10 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -1033,10 +1046,10 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -1045,10 +1058,10 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -1057,105 +1070,105 @@
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="18">
-        <v>3</v>
+        <v>54</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>81</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="22">
-        <v>8</v>
+        <v>55</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>82</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="22">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="869" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD1FC67E-6A2E-47C1-8B53-6AE35B4EE244}"/>
+  <xr:revisionPtr revIDLastSave="872" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B31F857C-3C98-4CD6-BE9A-4B0E16592EAB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -134,6 +134,9 @@
     <t>Beth yw mas proton?</t>
   </si>
   <si>
+    <t xml:space="preserve"> "1"</t>
+  </si>
+  <si>
     <t>Beth yw mas electron?</t>
   </si>
   <si>
@@ -143,9 +146,18 @@
     <t>Beth yw mas niwtron?</t>
   </si>
   <si>
+    <t>Pa rif yw'r RHIF ATOMIG? &lt;br&gt;&lt;br&gt; $\ce{^23_11Na}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "11"</t>
+  </si>
+  <si>
     <t>Pa rif yw'r RHIF MAS? &lt;br&gt;&lt;br&gt;$\ce{^23_11Na}$</t>
   </si>
   <si>
+    <t xml:space="preserve"> "23"</t>
+  </si>
+  <si>
     <t>Sawl proton sydd mewn &lt;br&gt;&lt;br&gt;$\ce{^23_11Na}$</t>
   </si>
   <si>
@@ -167,12 +179,30 @@
     <t>Beth yw'r nifer mwyaf o electronau sy'n gallu ffitio yn y plisgyn 1af?</t>
   </si>
   <si>
+    <t>"2"</t>
+  </si>
+  <si>
     <t>Beth yw'r nifer mwyaf o electronau sy'n gallu ffitio yn yr ail blisgyn?</t>
   </si>
   <si>
+    <t>"8"</t>
+  </si>
+  <si>
     <t>Beth yw'r nifer mwyaf o electronau sy'n gallu ffitio yn y trydydd plisgyn?</t>
   </si>
   <si>
+    <t>Eglurwch pa grŵp mae'r elfen sydd ag adeiledd electronig&lt;br&gt;&lt;br&gt;&lt;br&gt;2.8.5</t>
+  </si>
+  <si>
+    <t>Grŵp 5&lt;br&gt;oherwydd bod 3 electron yn y plisgyn ALLANOL</t>
+  </si>
+  <si>
+    <t>Eglurwch pa GYFNOD mae'r elfen sydd ag adeiledd electronig&lt;br&gt;&lt;br&gt;&lt;br&gt;2.8.3</t>
+  </si>
+  <si>
+    <t>Cyfnod 3&lt;br&gt; oherwydd bod 3 plisgyn o electronau</t>
+  </si>
+  <si>
     <t>Beth yw elfen?</t>
   </si>
   <si>
@@ -209,6 +239,9 @@
     <t>Rhowch gyfanswm nifer yr atomau sydd mewn moleciwl o nitrogen deuocsid</t>
   </si>
   <si>
+    <t>"3"</t>
+  </si>
+  <si>
     <t>Rhowch gyfanswm nifer yr atomau sydd mewn moleciwl o ethan</t>
   </si>
   <si>
@@ -254,50 +287,17 @@
     <t>lithiwm ac ocsigen</t>
   </si>
   <si>
-    <t>Rhowch yr ADWEITHYDDION sydd yn yr hafaiad yma &lt;br&gt;&lt;br&gt;,br&gt;lithiwm         +          ocsigen     --------&gt;   lithiwm ocsid</t>
+    <t>Rhowch yr ADWEITHYDDION sydd yn yr hafaiad yma &lt;br&gt;&lt;br&gt;&lt;br&gt;lithiwm         +          ocsigen     --------&gt;   lithiwm ocsid</t>
   </si>
   <si>
     <t>lithiwm ocsid</t>
-  </si>
-  <si>
-    <t>Grŵp 5&lt;br&gt;oherwydd bod 3 electron yn y plisgyn ALLANOL</t>
-  </si>
-  <si>
-    <t>Cyfnod 3&lt;br&gt; oherwydd bod 3 plisgyn o electronau</t>
-  </si>
-  <si>
-    <t>Pa rif yw'r RHIF ATOMIG? &lt;br&gt;&lt;br&gt; $\ce{^23_11Na}$</t>
-  </si>
-  <si>
-    <t>Eglurwch pa grŵp mae'r elfen sydd ag adeiledd electronig&lt;br&gt;&lt;br&gt;&lt;br&gt;2.8.5</t>
-  </si>
-  <si>
-    <t>Eglurwch pa GYFNOD mae'r elfen sydd ag adeiledd electronig&lt;br&gt;&lt;br&gt;&lt;br&gt;2.8.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "1"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "11"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "23"</t>
-  </si>
-  <si>
-    <t>"2"</t>
-  </si>
-  <si>
-    <t>"3"</t>
-  </si>
-  <si>
-    <t>"8"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -320,13 +320,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -381,12 +374,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -420,16 +407,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -444,19 +429,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,10 +459,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -680,496 +663,505 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="47" style="9"/>
-    <col min="2" max="2" width="47" style="22"/>
-    <col min="3" max="3" width="33.5703125" style="7" customWidth="1"/>
-    <col min="4" max="16384" width="47" style="7"/>
+    <col min="1" max="1" width="47" style="7"/>
+    <col min="2" max="2" width="47" style="19"/>
+    <col min="3" max="3" width="33.5703125" style="6" customWidth="1"/>
+    <col min="4" max="16384" width="47" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="21" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="8" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="21" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A20" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A35" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A36" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A37" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="22"/>
+    </row>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A38" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="22"/>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A39" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="22"/>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A40" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="18" t="s">
+      <c r="B40" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="18" t="s">
+      <c r="C40" s="22"/>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A41" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="18" t="s">
+      <c r="B41" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="18" t="s">
+      <c r="C41" s="22"/>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A42" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>71</v>
-      </c>
+      <c r="C42" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1180,28 +1172,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57DDB98-DED6-44B3-9212-7621DBC6158B}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
     <col min="3" max="4" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:4" ht="30.75" customHeight="1">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="33" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1210,61 +1202,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608DC02D-A3BC-4E94-A0C9-91816C3DAF43}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="49.42578125" style="12" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="4" width="49.42578125" style="10" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-    </row>
-    <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" ht="25.5" customHeight="1">
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="4" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="5" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="6" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="7" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="8" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="9" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="10" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="11" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="12" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="13" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="14" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="15" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="16" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="17" ht="25.5" customHeight="1"/>
+    <row r="18" ht="25.5" customHeight="1"/>
+    <row r="19" ht="25.5" customHeight="1"/>
+    <row r="20" ht="25.5" customHeight="1"/>
+    <row r="21" ht="25.5" customHeight="1"/>
+    <row r="22" ht="25.5" customHeight="1"/>
+    <row r="23" ht="25.5" customHeight="1"/>
+    <row r="24" ht="25.5" customHeight="1"/>
+    <row r="25" ht="25.5" customHeight="1"/>
+    <row r="26" ht="25.5" customHeight="1"/>
+    <row r="27" ht="25.5" customHeight="1"/>
+    <row r="28" ht="25.5" customHeight="1"/>
+    <row r="29" ht="25.5" customHeight="1"/>
+    <row r="30" ht="25.5" customHeight="1"/>
+    <row r="31" ht="25.5" customHeight="1"/>
+    <row r="32" ht="25.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1273,55 +1265,55 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7390D3-77B8-417A-BF28-251115C36B48}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="12" customWidth="1"/>
-    <col min="2" max="4" width="40.7109375" style="12" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="57.42578125" style="10" customWidth="1"/>
+    <col min="2" max="4" width="40.7109375" style="10" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="3" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="4" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="5" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="6" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="7" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="8" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="9" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="10" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="11" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="12" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="13" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="14" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="15" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="16" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="17" ht="29.25" customHeight="1"/>
+    <row r="18" ht="29.25" customHeight="1"/>
+    <row r="19" ht="29.25" customHeight="1"/>
+    <row r="20" ht="29.25" customHeight="1"/>
+    <row r="21" ht="29.25" customHeight="1"/>
+    <row r="22" ht="29.25" customHeight="1"/>
+    <row r="23" ht="29.25" customHeight="1"/>
+    <row r="24" ht="29.25" customHeight="1"/>
+    <row r="25" ht="29.25" customHeight="1"/>
+    <row r="26" ht="29.25" customHeight="1"/>
+    <row r="27" ht="29.25" customHeight="1"/>
+    <row r="28" ht="29.25" customHeight="1"/>
+    <row r="29" ht="29.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1330,64 +1322,64 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C1C183-043C-4181-ABFC-6CC837CF0487}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="6" width="64.140625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="6" width="64.140625" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" ht="28.5" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-    </row>
-    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-    </row>
-    <row r="9" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-    </row>
-    <row r="10" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-    </row>
-    <row r="11" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" s="11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="3" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="4" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="5" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="6" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="7" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="8" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="12" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="13" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="14" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="15" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="16" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="17" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="18" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="19" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="20" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="21" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="22" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="23" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="24" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="25" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="26" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="27" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="28" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="29" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="30" s="9" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="31" s="9" customFormat="1" ht="27.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1396,85 +1388,85 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D33F75-CDBA-43E0-9D68-0D698FDC504D}">
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="68.140625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="52.140625" style="15" customWidth="1"/>
-    <col min="3" max="4" width="42.140625" style="15" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="68.140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" style="13" customWidth="1"/>
+    <col min="3" max="4" width="42.140625" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="16"/>
-    </row>
-    <row r="30" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" s="15" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="3" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="4" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="5" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="6" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="7" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="8" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="9" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="10" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="11" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="12" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="13" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="14" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="15" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="16" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="17" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="18" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="19" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="20" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="21" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="22" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="23" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="24" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="25" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="26" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="27" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="28" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="29" spans="2:2" ht="31.5" customHeight="1">
+      <c r="B29" s="14"/>
+    </row>
+    <row r="30" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="31" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="32" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="33" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="34" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="35" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="36" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="37" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="38" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="39" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="40" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="41" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="42" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="43" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="44" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="45" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="46" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="47" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="48" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="49" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="50" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="51" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="52" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="53" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="54" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="55" s="13" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="56" s="13" customFormat="1" ht="31.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1483,66 +1475,66 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A950653-FD65-41B9-B4CE-86A2AB4CA7C0}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="4" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:9" ht="24.75" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-    </row>
-    <row r="2" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="3" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="4" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="5" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="6" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="7" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="8" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="9" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="10" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="11" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="12" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="13" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="14" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="15" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="16" spans="1:9" ht="24.75" customHeight="1"/>
+    <row r="17" ht="24.75" customHeight="1"/>
+    <row r="18" ht="24.75" customHeight="1"/>
+    <row r="19" ht="24.75" customHeight="1"/>
+    <row r="20" ht="24.75" customHeight="1"/>
+    <row r="21" ht="24.75" customHeight="1"/>
+    <row r="22" ht="24.75" customHeight="1"/>
+    <row r="23" ht="24.75" customHeight="1"/>
+    <row r="24" ht="24.75" customHeight="1"/>
+    <row r="25" ht="24.75" customHeight="1"/>
+    <row r="26" ht="24.75" customHeight="1"/>
+    <row r="27" ht="24.75" customHeight="1"/>
+    <row r="28" ht="24.75" customHeight="1"/>
+    <row r="29" ht="24.75" customHeight="1"/>
+    <row r="30" ht="24.75" customHeight="1"/>
+    <row r="31" ht="24.75" customHeight="1"/>
+    <row r="32" ht="24.75" customHeight="1"/>
+    <row r="33" ht="24.75" customHeight="1"/>
+    <row r="34" ht="24.75" customHeight="1"/>
+    <row r="35" ht="24.75" customHeight="1"/>
+    <row r="36" ht="24.75" customHeight="1"/>
+    <row r="37" ht="24.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="872" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B31F857C-3C98-4CD6-BE9A-4B0E16592EAB}"/>
+  <xr:revisionPtr revIDLastSave="1012" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE0C8EB5-7195-4116-86BB-BF3489F50B29}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1 Y Tabl Cyfnodol ar Atom" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="161">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -291,13 +291,247 @@
   </si>
   <si>
     <t>lithiwm ocsid</t>
+  </si>
+  <si>
+    <t>Beth sy'n cael ei wahanu gyda dull A? &lt;br&gt;Beth yw enw dull A?</t>
+  </si>
+  <si>
+    <t>Llifynnau (dyes), Inc&lt;br&gt; Cromatograffaeth (Chromatography)</t>
+  </si>
+  <si>
+    <t>Gwahanu.png</t>
+  </si>
+  <si>
+    <t>Beth sy'n cael ei wahanu gyda dull B? &lt;br&gt;Beth yw enw dull B?</t>
+  </si>
+  <si>
+    <t>Solid a hylif&lt;br&gt; Hidlo</t>
+  </si>
+  <si>
+    <t>Hydoddiant e.e. Halen a dŵr&lt;br&gt;Anweddu</t>
+  </si>
+  <si>
+    <t>Beth yw enw'r dull?</t>
+  </si>
+  <si>
+    <t>Distyllu</t>
+  </si>
+  <si>
+    <t>Distyllu.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dŵr ac ethanol yw J a K. Pa un yw'r J? </t>
+  </si>
+  <si>
+    <t>Ethanol</t>
+  </si>
+  <si>
+    <t>Pam fod dŵr ac ethanol yn gallu cael eu gwahanu trwy ddistyllu?</t>
+  </si>
+  <si>
+    <t>Berwbwynt dŵr yn uwch na ethanol</t>
+  </si>
+  <si>
+    <t>Pa pigment sydd fwyaf hydawdd?</t>
+  </si>
+  <si>
+    <t>2 gan ei fod wedi teithio bellaf i fyny'r papur</t>
+  </si>
+  <si>
+    <t>Cromatograffaeth.png</t>
+  </si>
+  <si>
+    <t>Cyfrifwch gwerth Rf pigment 2.</t>
+  </si>
+  <si>
+    <t>Rf = 7/10 = 0.7</t>
+  </si>
+  <si>
+    <t>Sut mae adnabod yr un pigmentau ar gromatogram?</t>
+  </si>
+  <si>
+    <t>Mae pigment sydd yr un lliw yn teithio yr un pellter i fyny'r papur.</t>
+  </si>
+  <si>
+    <t>Beth yw'r arsylwadau pan fydd metelau grŵp 1 yn cael eu torri mewn aer?</t>
+  </si>
+  <si>
+    <t>Maent yn edrych yn sgleiniog ond yna yn TARNEISIO (troi'n ddwl) yn gyflym.&lt;br&gt;&lt;br&gt; poasiwm yn gyflymach na sodiwm sydd yn gyflaymach na lithiwm</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith lithiwm gyda dŵr.</t>
+  </si>
+  <si>
+    <t>Symud ar wyneb y dŵr (arnofio a symud)&lt;br&gt;eferwi/ffisian</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith sodiwm gyda dŵr.</t>
+  </si>
+  <si>
+    <t>Symud yn gyflymach na lithiwm ar wyneb y dŵr&lt;br&gt;eferwi/ffisian&lt;br&gt;YMDODDI yn siâp pêl</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith potasiwm gyda dŵr.</t>
+  </si>
+  <si>
+    <t>Symud yn gyflymach na sodiwm ar wyneb y dŵr&lt;br&gt;eferwi/ffisian&lt;br&gt;ymdoddi yn siâp pêl&lt;br&gt;LLOSGI gyda FFLAM LELOG</t>
+  </si>
+  <si>
+    <t>Beth yw'r rhagofalon diogelwch sydd rhaid eu cymryd pa yn rhoi lithiwm, sodiwm neu potasiwm mewn dŵr?</t>
+  </si>
+  <si>
+    <t>DEFNYDDIO DARN BACH O'R METEL&lt;br&gt;DEFYDDIO CYFAINT MAWR O DDWR&lt;br&gt;defnyddio gefail i afael yn y metelau&lt;br&gt;gwisgo sbectol ddiogelwch a defnyddio sgrin plastig</t>
+  </si>
+  <si>
+    <t>Beth yw CYNHYRCHION adwaith lithiwm gyda dŵr?</t>
+  </si>
+  <si>
+    <t>lithiwm hydrocsid a hydrogen</t>
+  </si>
+  <si>
+    <t>Pa liw yw dangosydd pH mewn hydoddiant sodiwm hydrocsid (ar ôl adwaith sodiwm efo dŵr)?</t>
+  </si>
+  <si>
+    <t>porffor/piws/glas tywyll&lt;br&gt;pH11-14</t>
+  </si>
+  <si>
+    <t>Beth yw'r prawf am hydrogen?</t>
+  </si>
+  <si>
+    <t>Prenyn wedi ei gynnau (ar dân) yn gwneud sŵn 'pop' gwichlyd.</t>
+  </si>
+  <si>
+    <t>Beth yw'r tuedd mewn adweithedd i lawr grŵp 1?</t>
+  </si>
+  <si>
+    <t>Mynd yn fwy adweithiol i lawr y grŵp.&lt;br&gt;Haen UWCH - Wrth fynd i lawr y grŵp mae'r electron allanol yn mynd ymhellach o'r niwclews felly atyniad yn lleihau felly haws colli'r electron.</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith lithiwm pan yn llosgi mewn aer (gyda ocsigen).</t>
+  </si>
+  <si>
+    <t>Llosgi gyda fflam GOCH</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith sodiwm pan yn llosgi mewn aer (gyda ocsigen).</t>
+  </si>
+  <si>
+    <t>Llosgi gyda fflam FELYN</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith potasiwm pan yn llosgi mewn aer (gyda ocsigen).</t>
+  </si>
+  <si>
+    <t>Llosgi gyda fflam LELOG</t>
+  </si>
+  <si>
+    <t>Beth yw fformiwla sodiwm ocsid?</t>
+  </si>
+  <si>
+    <t>$Na-2O$</t>
+  </si>
+  <si>
+    <t>Beth yw fformiwla potasiwm hydrocsid?</t>
+  </si>
+  <si>
+    <t>KOH</t>
+  </si>
+  <si>
+    <t>Beth yw fformiwla nwy hydrogen?</t>
+  </si>
+  <si>
+    <t>$H-2$</t>
+  </si>
+  <si>
+    <t>Cydbwyso hafaliad.png</t>
+  </si>
+  <si>
+    <t>Ateb Cydbwyso hafaliad.png</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith lithiwm pan yn adweithio gyda clorin</t>
+  </si>
+  <si>
+    <t>Llosgi gyda fflam GOCH &lt;br&gt;ffurfio mwg gwyn o lithiwm clorid</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith sodiwm pan yn adweithio gyda clorin</t>
+  </si>
+  <si>
+    <t>Llosgi gyda fflam FELYN  &lt;br&gt;ffurfio mwg gwyn o sodiwm clorid</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith potasiwm pan yn adweithio gyda clorin</t>
+  </si>
+  <si>
+    <t>Llosgi gyda fflam LELOG  &lt;br&gt;ffurfio mwg gwyn o potasiwm clorid</t>
+  </si>
+  <si>
+    <t>Beth yw'r rhagofalon diogelwch sydd rhaid eu cymryd pa yn adweithio lithiwm, sodiwm neu potasiwm gyda clorin?</t>
+  </si>
+  <si>
+    <t>GWNEUD YR ARBRAWF MEWN CWPWRDD GWYNTYLLU gan fod clorin yn WENWYNIG&lt;br&gt;DEFNYDDIO DARN BACH O'R METEL&lt;br&gt;defnyddio gefail i afael yn y metelau&lt;br&gt;gwisgo sbectol ddiogelwch</t>
+  </si>
+  <si>
+    <t>Disgrifiwch adwaith clorin, bromin ac iodin gyda gwlan haearn.</t>
+  </si>
+  <si>
+    <t>Haearn yn MUDLOSGI a Mwg/solid browm oren goch o'r haearn clorid, haearn bromid, haearn iodid yn ffurfio&lt;br&gt;&lt;br&gt;clorin yn fwy adweithiol na bromin a bromin yn fwy adweithiol na iodin&lt;br&gt;&lt;br&gt;felly angen gwresogi yr haearn mewn bromin ychydig mwy a gwresogi llawer ar yr iodin a haearn</t>
+  </si>
+  <si>
+    <t>I beth mae clorin yn cael ei ddefnyddio?</t>
+  </si>
+  <si>
+    <t>I ladd bacteria mewn dŵr yfed a dŵr pyllau nofio/'hot tubs' ac i wneud cannydd (bleach) oherwydd ei fod yn WENWYNIG</t>
+  </si>
+  <si>
+    <t>I beth mae iodin yn cael ei ddefnyddio?</t>
+  </si>
+  <si>
+    <t>Fel ANTISEPTIG i ladd bacteria ar friw a cyn llawdriniaeth (operation) oherwydd ei fod yn WENWYNIG</t>
+  </si>
+  <si>
+    <t>Beth yw prawf am IONAU $Li^+$ , $Na^+$ , $K^+$ mewn cyfnsoddyn?</t>
+  </si>
+  <si>
+    <t>Prawf fflam - rhoi sampl o'r cyfansoddyn mewn fflam Bunsen&lt;br&gt;&lt;br&gt; lithium - fflam GOCH&lt;br&gt;sodiwm - fflam FELYN&lt;br&gt; potasiwm - fflam LELOG</t>
+  </si>
+  <si>
+    <t>Beth yw prawf am IONAU:&lt;br&gt;&lt;br&gt; CLORID $Cl^-$ &lt;br&gt;&lt;br&gt; BROMID $Br^-$ &lt;br&gt;&lt;br IODID $I^-$ mewn cyfansoddyn?</t>
+  </si>
+  <si>
+    <t>Gwneud hydoddiant o'r cyfansoddyn trwy ychwanegu dŵr&lt;br&gt; yna ychwanegu HYDODDIANT ARIAN NITRAD&lt;br&gt;&lt;br&gt;CLORID - GWADDOD GWYN&lt;br&gt;&lt;br&gt; BROMID - GWADDOD LLIW HUFEN&lt;br&gt;&lt;br&gt;IODID - GWADDOD MELYN</t>
+  </si>
+  <si>
+    <t>40 + 32 + 16 + 16 + 16 + 16 = 136</t>
+  </si>
+  <si>
+    <t>Cyfrifo Mr.png</t>
+  </si>
+  <si>
+    <t>(i)  1 + 35.5 + 16 = 52.5 &lt;br&gt;&lt;br&gt; &lt;br&gt;(ii)  32/64 x 100 = 50%</t>
+  </si>
+  <si>
+    <t>Cyfrifo canran elfen.png</t>
+  </si>
+  <si>
+    <t>Mr $K_2 CO_3$ = 39 + 39 + 12 + 16 + 16 + 16 = 138</t>
+  </si>
+  <si>
+    <t>Canran carbon.png</t>
+  </si>
+  <si>
+    <t>3.13 / 4.35 x 100 = 72%</t>
+  </si>
+  <si>
+    <t>Canran cynnyrch.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -374,6 +608,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -402,7 +642,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -444,6 +684,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1193,6 +1437,102 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="33" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1201,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608DC02D-A3BC-4E94-A0C9-91816C3DAF43}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="49.42578125" style="10" customWidth="1"/>
@@ -1225,38 +1565,220 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1">
-      <c r="D2" s="11"/>
-    </row>
-    <row r="3" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="4" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="5" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="6" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="7" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="8" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="9" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="10" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="11" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="12" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="13" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="14" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="15" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="16" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="17" ht="25.5" customHeight="1"/>
-    <row r="18" ht="25.5" customHeight="1"/>
-    <row r="19" ht="25.5" customHeight="1"/>
-    <row r="20" ht="25.5" customHeight="1"/>
-    <row r="21" ht="25.5" customHeight="1"/>
-    <row r="22" ht="25.5" customHeight="1"/>
-    <row r="23" ht="25.5" customHeight="1"/>
-    <row r="24" ht="25.5" customHeight="1"/>
-    <row r="25" ht="25.5" customHeight="1"/>
-    <row r="26" ht="25.5" customHeight="1"/>
-    <row r="27" ht="25.5" customHeight="1"/>
-    <row r="28" ht="25.5" customHeight="1"/>
-    <row r="29" ht="25.5" customHeight="1"/>
-    <row r="30" ht="25.5" customHeight="1"/>
-    <row r="31" ht="25.5" customHeight="1"/>
-    <row r="32" ht="25.5" customHeight="1"/>
+      <c r="A2" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A3" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A12" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A13" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A15" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="25.5" customHeight="1">
+      <c r="C17" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A18" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A19" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A20" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A21" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A22" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A23" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A24" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A25" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A26" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="25.5" customHeight="1"/>
+    <row r="28" spans="1:4" ht="25.5" customHeight="1"/>
+    <row r="29" spans="1:4" ht="25.5" customHeight="1"/>
+    <row r="30" spans="1:4" ht="25.5" customHeight="1"/>
+    <row r="31" spans="1:4" ht="25.5" customHeight="1"/>
+    <row r="32" spans="1:4" ht="25.5" customHeight="1"/>
+    <row r="33" ht="25.5" customHeight="1"/>
+    <row r="34" ht="25.5" customHeight="1"/>
+    <row r="35" ht="25.5" customHeight="1"/>
+    <row r="36" ht="25.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1286,10 +1808,38 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="3" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="4" spans="1:4" ht="29.25" customHeight="1"/>
-    <row r="5" spans="1:4" ht="29.25" customHeight="1"/>
+    <row r="2" spans="1:4" ht="29.25" customHeight="1">
+      <c r="B2" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="29.25" customHeight="1">
+      <c r="B3" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="29.25" customHeight="1">
+      <c r="B4" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="29.25" customHeight="1">
+      <c r="B5" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
     <row r="6" spans="1:4" ht="29.25" customHeight="1"/>
     <row r="7" spans="1:4" ht="29.25" customHeight="1"/>
     <row r="8" spans="1:4" ht="29.25" customHeight="1"/>

--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1012" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE0C8EB5-7195-4116-86BB-BF3489F50B29}"/>
+  <xr:revisionPtr revIDLastSave="1071" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9D56F44-7830-4268-A8D2-F912790ACAD9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1 Y Tabl Cyfnodol ar Atom" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="2.3 Dwr" sheetId="4" r:id="rId5"/>
     <sheet name="2.4 Y Ddaear" sheetId="7" r:id="rId6"/>
     <sheet name="2.5 Cyfradd Adwaith" sheetId="8" r:id="rId7"/>
+    <sheet name="1.6 Calchfaen" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="187">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -356,7 +357,7 @@
     <t>Beth yw'r arsylwadau pan fydd metelau grŵp 1 yn cael eu torri mewn aer?</t>
   </si>
   <si>
-    <t>Maent yn edrych yn sgleiniog ond yna yn TARNEISIO (troi'n ddwl) yn gyflym.&lt;br&gt;&lt;br&gt; poasiwm yn gyflymach na sodiwm sydd yn gyflaymach na lithiwm</t>
+    <t>Maent yn edrych yn sgleiniog ond yna yn TARNEISIO (troi'n ddwl) yn gyflym.&lt;br&gt;&lt;br&gt; potasiwm yn gyflymach na sodiwm sydd yn gyflymach na lithiwm</t>
   </si>
   <si>
     <t>Disgrifiwch adwaith lithiwm gyda dŵr.</t>
@@ -428,7 +429,7 @@
     <t>Beth yw fformiwla sodiwm ocsid?</t>
   </si>
   <si>
-    <t>$Na-2O$</t>
+    <t>$Na_2O$</t>
   </si>
   <si>
     <t>Beth yw fformiwla potasiwm hydrocsid?</t>
@@ -440,7 +441,10 @@
     <t>Beth yw fformiwla nwy hydrogen?</t>
   </si>
   <si>
-    <t>$H-2$</t>
+    <t>$H_2$</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
   <si>
     <t>Cydbwyso hafaliad.png</t>
@@ -491,13 +495,13 @@
     <t>Fel ANTISEPTIG i ladd bacteria ar friw a cyn llawdriniaeth (operation) oherwydd ei fod yn WENWYNIG</t>
   </si>
   <si>
-    <t>Beth yw prawf am IONAU $Li^+$ , $Na^+$ , $K^+$ mewn cyfnsoddyn?</t>
+    <t>Beth yw'r prawf am IONAU $Li^+$ , $Na^+$ , $K^+$ mewn cyfnsoddyn?</t>
   </si>
   <si>
     <t>Prawf fflam - rhoi sampl o'r cyfansoddyn mewn fflam Bunsen&lt;br&gt;&lt;br&gt; lithium - fflam GOCH&lt;br&gt;sodiwm - fflam FELYN&lt;br&gt; potasiwm - fflam LELOG</t>
   </si>
   <si>
-    <t>Beth yw prawf am IONAU:&lt;br&gt;&lt;br&gt; CLORID $Cl^-$ &lt;br&gt;&lt;br&gt; BROMID $Br^-$ &lt;br&gt;&lt;br IODID $I^-$ mewn cyfansoddyn?</t>
+    <t>Beth yw'r prawf am IONAU:&lt;br&gt;&lt;br&gt; CLORID $Cl^-$ &lt;br&gt;&lt;br&gt; BROMID $Br^-$ &lt;br&gt;&lt;br&gt;IODID $I^-$ mewn cyfansoddyn?</t>
   </si>
   <si>
     <t>Gwneud hydoddiant o'r cyfansoddyn trwy ychwanegu dŵr&lt;br&gt; yna ychwanegu HYDODDIANT ARIAN NITRAD&lt;br&gt;&lt;br&gt;CLORID - GWADDOD GWYN&lt;br&gt;&lt;br&gt; BROMID - GWADDOD LLIW HUFEN&lt;br&gt;&lt;br&gt;IODID - GWADDOD MELYN</t>
@@ -525,6 +529,86 @@
   </si>
   <si>
     <t>Canran cynnyrch.png</t>
+  </si>
+  <si>
+    <t>Disgrifiwch y cam gwaddodi yn y broses trin dŵr.</t>
+  </si>
+  <si>
+    <t>gadael y dŵr i sefyll/setlo mewn tanciau&lt;br&gt;&lt;br&gt;cael gwared ar gronynnau mawr anhydawdd oherwydd eu bod yn yn suddo i'r gwaelod oherwydd disgyrchiant</t>
+  </si>
+  <si>
+    <t>Trin dwr.png</t>
+  </si>
+  <si>
+    <t>Disgrifiwch y cam hidlo yn y broses trin dŵr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pasio'r dŵr drwy dywod a graean&lt;br&gt;&lt;br&gt;cael gwared â gronynnau anhydawdd llai </t>
+  </si>
+  <si>
+    <t>Disgrifiwch y cam clorineiddio yn y broses trin dŵr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ychwanegu clorin i ladd bacteria a firysau&lt;br&gt;&lt;br&gt;atal clefyd e.e. colera / teiffoid / norofirws
+</t>
+  </si>
+  <si>
+    <t>Pam fod fflworid yn cael ei ychwanegu i ddŵr yfed mewn rhai ardaloedd?</t>
+  </si>
+  <si>
+    <t>i gryfhau enamel dannedd&lt;br&gt;&lt;br&gt; i leihau pydredd dannedd&lt;br&gt;&lt;br&gt;ac felly lleihau llenwadau/tyllau (fillings)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pam fod rhai pobl yn credu na ddylai fflworid gael ei ychwanegu at ddŵr yfed? </t>
+  </si>
+  <si>
+    <t>mae'n feddyginiaethu torfol / does gennych chi ddim
+dewis&lt;br&gt;&lt;br&gt;fflworosis /
+mae'n gwneud eich dannedd yn felyn neu smotiau&lt;br&gt;&lt;br&gt;gallwch chi gael digon o fflworid mewn past dannedd
+neu dabledi&lt;br&gt;&lt;br&gt; mae'n bosibl ei fod yn gysylltiedig â phroblemau'r
+stumog / esgyrn</t>
+  </si>
+  <si>
+    <t>Pam fod hi'n bwysig bod ocsigen mewn ffynonellau dŵr naturiol fel llynnoedd?</t>
+  </si>
+  <si>
+    <t>Er mwyn i blanhigion ac anifeiliad sy'n byw yn y dŵr resbiradu.</t>
+  </si>
+  <si>
+    <t>Pam fod hi'n bwysig bod carbon deuocsid mewn ffynonellau dŵr naturiol fel llynnoedd?</t>
+  </si>
+  <si>
+    <t>Er mwyn i blanhigion sy'n byw yn y dŵr allu gwneud ffotosynthesis</t>
+  </si>
+  <si>
+    <t>Pa ionau sy'n gwneud dŵr caled yn galed?</t>
+  </si>
+  <si>
+    <t>$Mg^2+$  $Ca^"+$</t>
+  </si>
+  <si>
+    <t>Sut mae cael gwared ar ddŵr caled dros dro?</t>
+  </si>
+  <si>
+    <t>Ei ferwi</t>
+  </si>
+  <si>
+    <t>Beth yw dŵr caled?</t>
+  </si>
+  <si>
+    <t>Dŵr sydd ddim yn ffurfio trochion (swigod) yn hawdd gyda sebon</t>
+  </si>
+  <si>
+    <t>Manteision dŵr caled</t>
+  </si>
+  <si>
+    <t>cryfhau dannedd ac esgyrn&lt;br&gt;&lt;br&gt;lleihau'r risg o glefyd y galon&lt;br&gt;&lt;br&gt;blasu'n well na dŵr meddal</t>
+  </si>
+  <si>
+    <t>Anfanteision dŵr caled</t>
+  </si>
+  <si>
+    <t>defnyddio mwy o sebon&lt;br&gt;&lt;br&gt;ffurfio calchgen wrth ei wresogi sydd yn blocio pibellau ac offer cynhesu dŵr&lt;br&gt;&lt;br&gt;Mae'n ffurfio llysnafedd (scum) gyda sebon</t>
   </si>
 </sst>
 </file>
@@ -685,7 +769,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1544,7 +1628,9 @@
   <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="49.42578125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="49.42578125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="90" style="10" customWidth="1"/>
+    <col min="3" max="4" width="49.42578125" style="10" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
@@ -1690,83 +1776,89 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A17" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>133</v>
+      </c>
       <c r="C17" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="25.5" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="25.5" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="25.5" customHeight="1">
       <c r="A20" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="25.5" customHeight="1">
       <c r="A21" s="23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="25.5" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="25.5" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="25.5" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="25.5" customHeight="1">
       <c r="A25" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="25.5" customHeight="1">
       <c r="A26" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="25.5" customHeight="1"/>
@@ -1810,34 +1902,34 @@
     </row>
     <row r="2" spans="1:4" ht="29.25" customHeight="1">
       <c r="B2" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29.25" customHeight="1">
       <c r="B3" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="29.25" customHeight="1">
       <c r="B4" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="29.25" customHeight="1">
       <c r="B5" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.25" customHeight="1"/>
@@ -1874,7 +1966,9 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="6" width="64.140625" style="9" customWidth="1"/>
+    <col min="1" max="2" width="64.140625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="26" style="9" customWidth="1"/>
+    <col min="4" max="6" width="64.140625" style="9" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
@@ -1894,24 +1988,111 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="3" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="4" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="5" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="6" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="7" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="2" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A2" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A5" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A6" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A8" s="10"/>
+      <c r="A8" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A9" s="10"/>
+      <c r="A9" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="12" spans="1:6" ht="27.75" customHeight="1"/>
-    <row r="13" spans="1:6" ht="27.75" customHeight="1"/>
+      <c r="A10" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
     <row r="14" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="15" spans="1:6" ht="27.75" customHeight="1"/>
     <row r="16" spans="1:6" ht="27.75" customHeight="1"/>
@@ -2088,4 +2269,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C18B3CD-C674-494F-83D8-310B8A0DB0B6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1071" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9D56F44-7830-4268-A8D2-F912790ACAD9}"/>
+  <xr:revisionPtr revIDLastSave="1172" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E08C24F3-B344-4CBF-9A8E-D252C8E00E57}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1 Y Tabl Cyfnodol ar Atom" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="242">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -610,12 +610,177 @@
   <si>
     <t>defnyddio mwy o sebon&lt;br&gt;&lt;br&gt;ffurfio calchgen wrth ei wresogi sydd yn blocio pibellau ac offer cynhesu dŵr&lt;br&gt;&lt;br&gt;Mae'n ffurfio llysnafedd (scum) gyda sebon</t>
   </si>
+  <si>
+    <t>Rhestrwch gwahanol haenau adeiledd y Ddaear o'r canol</t>
+  </si>
+  <si>
+    <t>Craidd mewnol&lt;br&gt;Craidd allanol&lt;br&gt;Mantell&lt;br&gt;Cramen</t>
+  </si>
+  <si>
+    <t>Rhestrwch 3 damcaniaeth Alfred Wegener o'r drifft cyfandirol (y cyfandiroedd yn symud)</t>
+  </si>
+  <si>
+    <t>Siâp y cyfandiroedd gwahanol yn ffitio fel jigsô&lt;br&gt;&lt;br&gt;Bod creigiau o'r un math ac oed ar gyfandiroedd gwahanol&lt;br&gt;&lt;br&gt;Bod ffosiliau o'r un anifeiliad a phlanhigion ar gyfandiroedd gwahanol</t>
+  </si>
+  <si>
+    <t>Pam nad oedd pobl yn credu damcaniaeth Wegeger?</t>
+  </si>
+  <si>
+    <t>Doedd Wegener ddim yn gallu egluro sut roedd y cyfandiroedd yn symud</t>
+  </si>
+  <si>
+    <t>Beth yw enw'r darnau mawr sy'n ffurfio cramen y Ddaear?</t>
+  </si>
+  <si>
+    <t>Platiau Tectonig</t>
+  </si>
+  <si>
+    <t>Beth oedd enw'r un darn o dir pan oedd yr holl gyfandiroedd wedi eu huno (joined)?</t>
+  </si>
+  <si>
+    <t>Pangaea</t>
+  </si>
+  <si>
+    <t>Beth sy'n achosi i'r platiau tectonig symud?</t>
+  </si>
+  <si>
+    <t>Ceryntau Darfudiad yn y magma yn mantell y Ddaear</t>
+  </si>
+  <si>
+    <t>Disgrifiwch beth sy'n digwydd wrth ffin platiau ADEILADOL</t>
+  </si>
+  <si>
+    <t>Platiau yn symud oddi wrth ei gilydd oherwydd cerrynt darfudiad yn y magma&lt;br&gt;&lt;br&gt;Magma yn codi i'r bwlch rhwng y platiau&lt;br&gt;&lt;br&gt;Magma yn oeri a caledu i ffurfio craig newydd&lt;br&gt;&lt;br&gt;Mae Llosgfynydd (echdoriad folcanig) a daeargrynfeydd</t>
+  </si>
+  <si>
+    <t>Ffin adeiladol.png</t>
+  </si>
+  <si>
+    <t>Disgrifiwch beth sy'n digwydd wrth ffin platiau DINISTRIOL (DISTRYWIOL)</t>
+  </si>
+  <si>
+    <t>Platiau yn symud tuag at ei gilydd oherwydd cerrynt darfudiad yn y magma&lt;br&gt;&lt;br&gt;Y plat cefnforol MWY DWYS yn cael ei wthio o dan y plat cyfandirol&lt;br&gt;&lt;br&gt;Y plat sydd wedi suddo yn ymdoddi i ffufio magma &lt;br&gt;&lt;br&gt;Mae Llosgfynydd (echdoriad folcanig) a daeargrynfeydd</t>
+  </si>
+  <si>
+    <t>Ffin dinistriol.png</t>
+  </si>
+  <si>
+    <t>Disgrifiwch beth sy'n digwydd wrth ffin platiau CADWROL</t>
+  </si>
+  <si>
+    <t>Y platiau yn llithro yn erbyn ei gilydd&lt;br&gt;&lt;br&gt;gan achosi ffrithiant&lt;br&gt;&lt;br&gt;Dim ond yn achosi daeargrynfeydd</t>
+  </si>
+  <si>
+    <t>Pa blatiau sy'n ffin adeiladol?</t>
+  </si>
+  <si>
+    <t>1 a 4&lt;br&gt;&lt;br&gt;5 a 6</t>
+  </si>
+  <si>
+    <t>Map ffiniau.png</t>
+  </si>
+  <si>
+    <t>Pa blatiau sy'n ffin dinistriol?</t>
+  </si>
+  <si>
+    <t>1 a 7&lt;br&gt;&lt;br&gt;3 a 5</t>
+  </si>
+  <si>
+    <t>Pa blatiau sy'n ffin cadwrol?</t>
+  </si>
+  <si>
+    <t>2 a 8&lt;br&gt;&lt;br&gt;3 a'r plât bach yn y canol heb rif (y Dwyrain Canol)</t>
+  </si>
+  <si>
+    <t>Beth yw'r canran o nitrogen ac ocsigen yn yr atmosffer presennol?</t>
+  </si>
+  <si>
+    <t>Nitrogen 78%&lt;br&gt;&lt;br&gt;Ocsigen 21%</t>
+  </si>
+  <si>
+    <t>Pa nwyon oedd yn atmosffer cynnar y Ddaear?</t>
+  </si>
+  <si>
+    <t>Carbon deuocsid&lt;br&gt;&lt;br&gt;Carbon deuocsid&lt;br&gt;&lt;br&gt;Anwedd dŵr</t>
+  </si>
+  <si>
+    <t>Sut wnaeth swm (amount) yr anwedd dŵr leihau?</t>
+  </si>
+  <si>
+    <t>Y Ddaear yn OERI&lt;br&gt;&lt;br&gt;yr anwedd dŵr yn CYDDWYSO ac felly yn glawio&lt;br&gt;&lt;br&gt;cefnforoedd (oceans) yn ffurfio</t>
+  </si>
+  <si>
+    <t>Sut wnaeth swm (amount) y carbon deuocsid leihau?</t>
+  </si>
+  <si>
+    <t>Planhigion wedi esblygu sy'n defnyddio'r carbon deuocsid mewn FFOTOSYNTHESIS&lt;br&gt;&lt;br&gt;Rhywfaint ohono yn hydoddi mewn cefnforoedd&lt;br&gt;&lt;br&gt;yna wedi ei gloi mewn tanwyddau ffosil a chreigiau</t>
+  </si>
+  <si>
+    <t>Sut wnaeth yr amonia leihau/diflannu?</t>
+  </si>
+  <si>
+    <t>amonia wedi adweithio efo ocsigen i ffurfio nitrogen</t>
+  </si>
+  <si>
+    <t>Beth yw'r ddwy broses sy'n digwydd ar y Ddaear sy'n amsugno ocsigen i ffurfio carbon deuocsid ac egni?</t>
+  </si>
+  <si>
+    <t>Resbiradaeth a hylosgiad</t>
+  </si>
+  <si>
+    <t>Hafaliadau resbiradaeth, hylosgi, ffotosynthesis.png</t>
+  </si>
+  <si>
+    <t>Beth yw'r broses sy'n digwydd ar y Ddaear sy'n amsugno carbon deuocsid ac egni i ffurfio ocsigen?</t>
+  </si>
+  <si>
+    <t>Ffotosynthesis</t>
+  </si>
+  <si>
+    <t>Pam fod canran y carbon deuocsid ar y Ddaear yn cynyddu?</t>
+  </si>
+  <si>
+    <t>Hylosgi / llosgi mwy o danwyddau fforisl fel glo, olew  a nwy&lt;br&gt;&lt;br&gt; Datgoedwigo (torri llawer iawn o goed i lawr) felly llai o ffotosynthesis</t>
+  </si>
+  <si>
+    <t>Beth sy'n digwydd oherwydd y cynnydd mewn carbon deuocsid?</t>
+  </si>
+  <si>
+    <t>Cynhesu Byd Eang&lt;br&gt;&lt;br&gt;haen o nwyon ty gwydr yn cynyddu felly mwy o wres yn cael ddal yn yr atmosffer</t>
+  </si>
+  <si>
+    <t>Beth sy'n digwydd oherwydd effaith cynhesu byd eang?</t>
+  </si>
+  <si>
+    <t>Newid hinsawdd (mwy o law/mwy o sychder/ tywydd mwy eithafol)&lt;br&gt;&lt;br&gt;Pegynnau iâ yn ymdoddi - lefel y môr yn codi - llifogydd</t>
+  </si>
+  <si>
+    <t>Sut allwn ni leihau effaith cynhesu byd eang?</t>
+  </si>
+  <si>
+    <t>Llosgi llai o danwyddau ffosil&lt;br&gt;&lt;br&gt;defnyddio ffynonellau egni adnewyddadwy (renewable)&lt;br&gt;&lt;br&gt;plannu mwy o goed a torri llai o goed</t>
+  </si>
+  <si>
+    <t>Prawf am y nwy hydrogen?</t>
+  </si>
+  <si>
+    <t>pop' gwichlyd wrth roi sblint wedi ei gynnau (ar dân) mewn hydrogen</t>
+  </si>
+  <si>
+    <t>Prawf am y nwy ocsigen?</t>
+  </si>
+  <si>
+    <t>sblint yn mudlosgi yn ail-gynnau (relights) mewn ocsigen</t>
+  </si>
+  <si>
+    <t>Prawf am y nwy carbon deuocsid?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -698,6 +863,13 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -726,7 +898,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -770,6 +942,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2141,39 +2319,242 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="3" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="4" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="5" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="6" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="7" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="8" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="9" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="10" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="11" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="12" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="13" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="14" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="15" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="16" spans="1:4" ht="31.5" customHeight="1"/>
-    <row r="17" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="18" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="19" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="20" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="21" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="22" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="23" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="24" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="25" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="26" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="27" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="28" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="29" spans="2:2" ht="31.5" customHeight="1">
+    <row r="2" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A6" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A7" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A8" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A9" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A10" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A11" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A12" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A13" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A14" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A15" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A16" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A17" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A19" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A20" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A21" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A22" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A23" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A24" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A25" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A26" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A27" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="29" spans="1:4" ht="31.5" customHeight="1">
       <c r="B29" s="14"/>
     </row>
-    <row r="30" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="31" spans="2:2" ht="31.5" customHeight="1"/>
-    <row r="32" spans="2:2" ht="31.5" customHeight="1"/>
+    <row r="30" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="31" spans="1:4" ht="31.5" customHeight="1"/>
+    <row r="32" spans="1:4" ht="31.5" customHeight="1"/>
     <row r="33" s="13" customFormat="1" ht="31.5" customHeight="1"/>
     <row r="34" s="13" customFormat="1" ht="31.5" customHeight="1"/>
     <row r="35" s="13" customFormat="1" ht="31.5" customHeight="1"/>

--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1172" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E08C24F3-B344-4CBF-9A8E-D252C8E00E57}"/>
+  <xr:revisionPtr revIDLastSave="1189" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A37725D8-000C-4422-A271-F57B89BF498B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1 Y Tabl Cyfnodol ar Atom" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="248">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -195,7 +195,7 @@
     <t>Eglurwch pa grŵp mae'r elfen sydd ag adeiledd electronig&lt;br&gt;&lt;br&gt;&lt;br&gt;2.8.5</t>
   </si>
   <si>
-    <t>Grŵp 5&lt;br&gt;oherwydd bod 3 electron yn y plisgyn ALLANOL</t>
+    <t>Grŵp 5&lt;br&gt;oherwydd bod 5 electron yn y plisgyn ALLANOL</t>
   </si>
   <si>
     <t>Eglurwch pa GYFNOD mae'r elfen sydd ag adeiledd electronig&lt;br&gt;&lt;br&gt;&lt;br&gt;2.8.3</t>
@@ -507,25 +507,25 @@
     <t>Gwneud hydoddiant o'r cyfansoddyn trwy ychwanegu dŵr&lt;br&gt; yna ychwanegu HYDODDIANT ARIAN NITRAD&lt;br&gt;&lt;br&gt;CLORID - GWADDOD GWYN&lt;br&gt;&lt;br&gt; BROMID - GWADDOD LLIW HUFEN&lt;br&gt;&lt;br&gt;IODID - GWADDOD MELYN</t>
   </si>
   <si>
-    <t>40 + 32 + 16 + 16 + 16 + 16 = 136</t>
+    <t>"40 + 32 + 16 + 16 + 16 + 16 = 136"</t>
   </si>
   <si>
     <t>Cyfrifo Mr.png</t>
   </si>
   <si>
-    <t>(i)  1 + 35.5 + 16 = 52.5 &lt;br&gt;&lt;br&gt; &lt;br&gt;(ii)  32/64 x 100 = 50%</t>
+    <t>"(i)  1 + 35.5 + 16 = 52.5 &lt;br&gt;&lt;br&gt; &lt;br&gt;(ii)  32/64 x 100 = 50%"</t>
   </si>
   <si>
     <t>Cyfrifo canran elfen.png</t>
   </si>
   <si>
-    <t>Mr $K_2 CO_3$ = 39 + 39 + 12 + 16 + 16 + 16 = 138</t>
+    <t>"Mr $K_2 CO_3$ = 39 + 39 + 12 + 16 + 16 + 16 = 138"</t>
   </si>
   <si>
     <t>Canran carbon.png</t>
   </si>
   <si>
-    <t>3.13 / 4.35 x 100 = 72%</t>
+    <t>"3.13 / 4.35 x 100 = 72%"</t>
   </si>
   <si>
     <t>Canran cynnyrch.png</t>
@@ -774,6 +774,24 @@
   </si>
   <si>
     <t>Prawf am y nwy carbon deuocsid?</t>
+  </si>
+  <si>
+    <t>Dŵr calch yn troi'n llaethog pan fydd carbon deuocsid yn cael ei fyrlymu trwyddo</t>
+  </si>
+  <si>
+    <t>Defnydd nitrogen?</t>
+  </si>
+  <si>
+    <t>Cynhyrchu gwrtaith</t>
+  </si>
+  <si>
+    <t>Defnydd ocsigen?</t>
+  </si>
+  <si>
+    <t>Defnydd argon a neon?</t>
+  </si>
+  <si>
+    <t>Atmosffer anadweithiol mewn goleuadau, pacio bwydydd..</t>
   </si>
 </sst>
 </file>
@@ -2079,6 +2097,9 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A2" s="10" t="s">
+        <v>133</v>
+      </c>
       <c r="B2" s="10" t="s">
         <v>154</v>
       </c>
@@ -2087,6 +2108,9 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A3" s="10" t="s">
+        <v>133</v>
+      </c>
       <c r="B3" s="10" t="s">
         <v>156</v>
       </c>
@@ -2095,6 +2119,9 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>133</v>
+      </c>
       <c r="B4" s="10" t="s">
         <v>158</v>
       </c>
@@ -2103,6 +2130,9 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>133</v>
+      </c>
       <c r="B5" s="10" t="s">
         <v>160</v>
       </c>
@@ -2545,14 +2575,33 @@
         <v>241</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="31.5" customHeight="1"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A28" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
     <row r="29" spans="1:4" ht="31.5" customHeight="1">
-      <c r="B29" s="14"/>
-    </row>
-    <row r="30" spans="1:4" ht="31.5" customHeight="1"/>
+      <c r="A29" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A30" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
     <row r="31" spans="1:4" ht="31.5" customHeight="1"/>
     <row r="32" spans="1:4" ht="31.5" customHeight="1"/>
     <row r="33" s="13" customFormat="1" ht="31.5" customHeight="1"/>

--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1189" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A37725D8-000C-4422-A271-F57B89BF498B}"/>
+  <xr:revisionPtr revIDLastSave="1291" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF6CCB99-A144-426B-9416-B7EC4DAEAD7E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1 Y Tabl Cyfnodol ar Atom" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="299">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -623,7 +623,7 @@
     <t>Siâp y cyfandiroedd gwahanol yn ffitio fel jigsô&lt;br&gt;&lt;br&gt;Bod creigiau o'r un math ac oed ar gyfandiroedd gwahanol&lt;br&gt;&lt;br&gt;Bod ffosiliau o'r un anifeiliad a phlanhigion ar gyfandiroedd gwahanol</t>
   </si>
   <si>
-    <t>Pam nad oedd pobl yn credu damcaniaeth Wegeger?</t>
+    <t>Pam nad oedd pobl yn credu damcaniaeth Wegener?</t>
   </si>
   <si>
     <t>Doedd Wegener ddim yn gallu egluro sut roedd y cyfandiroedd yn symud</t>
@@ -792,13 +792,183 @@
   </si>
   <si>
     <t>Atmosffer anadweithiol mewn goleuadau, pacio bwydydd..</t>
+  </si>
+  <si>
+    <t>Beth yw'r ffactorau sy'n effeithio ar gyfradd adwaith?</t>
+  </si>
+  <si>
+    <t>Tymheredd&lt;br&gt;Crynodiad asid (hydoddiant)&lt;br&gt;Maint Darnau solid&lt;br&gt;Catalydd</t>
+  </si>
+  <si>
+    <t>Eglurwch sut mae tymheredd uwch yn effeithio ar gyfradd adwaith.</t>
+  </si>
+  <si>
+    <t>Cynyddu cyfradd adwaith&lt;br&gt;Mwy o egni gan y gronynnau&lt;br&gt;felly mwy o siawns o wrthdrawiadau llwyddiannus pob eiliad</t>
+  </si>
+  <si>
+    <t>Eglurwch sut mae crynodiad asid is yn effeithio ar gyfradd adwaith.</t>
+  </si>
+  <si>
+    <t>Lleihau cyfradd adwaith&lt;br&gt;Llai o gronynnau asid yn yr un cyfaint&lt;br&gt;felly llai o siawns o wrthdrawiadau llwyddiannus pob eiliad</t>
+  </si>
+  <si>
+    <t>Eglurwch sut mae defnyddio powdr yn lle darnau mawr o solid yn effeithio ar gyfradd adwaith.</t>
+  </si>
+  <si>
+    <t>Cynyddu cyfradd adwaith&lt;br&gt;Darnau llai gyda arwynebedd arwyneb mwy&lt;br&gt;felly mwy o siawns o wrthdrawiadau llwyddiannus pob eiliad</t>
+  </si>
+  <si>
+    <t>Beth yw catalydd?</t>
+  </si>
+  <si>
+    <t>Sylwedd sy'n cyflymu adwaith heb gael ei newid ei hun.</t>
+  </si>
+  <si>
+    <t>Disgrifiwch 3 ffordd o fesur cyfradd adwaith sy'n cynhyrchu nwy.</t>
+  </si>
+  <si>
+    <t>Mesur cyfaint y nwy neu mas y nwy sy'n cael ei golli pob 10 eiliad (rhaid cofio son am amser)</t>
+  </si>
+  <si>
+    <t>Dull cyfradd 1.png</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ffordd o fesur cyfradd adwaith sy'n cynhyrchu solid.</t>
+  </si>
+  <si>
+    <t>Amseru'r amser i'r groes 'ddiflannu'</t>
+  </si>
+  <si>
+    <t>Dull cyfradd 2.png</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ffordd o fesur cyfradd adwaith sy'n cynhyrchu solid heb ddefnyddio croes ar bapur yn diflannu</t>
+  </si>
+  <si>
+    <t>Wrth i'r solid ffurfio mae llai o olau yn teithio trwy'r cymysgedd at y canfodydd pob eiliad&lt;br&gt;&lt;br&gt;Mae'r calyniadau yn cael eu dangos ar graff</t>
+  </si>
+  <si>
+    <t>Dull cyfradd 3.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Esboniwch pa graff sy'n dangos adwaith ar dymheredd uwch na 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>℃.</t>
+    </r>
+  </si>
+  <si>
+    <t>B&lt;br&gt;&lt;br&gt;adwaith cyflymach -llinell mwy serth / adwaith wedi gorffen gyntaf (llinell wedi mynd yn wastad gyntaf)</t>
+  </si>
+  <si>
+    <t>Graff cyfradd.png</t>
+  </si>
+  <si>
+    <t>Eglurwch pa adwaith sydd fwyaf araf.</t>
+  </si>
+  <si>
+    <t>D&lt;br&gt;&lt;br&gt;Llinell lleiaf serth</t>
+  </si>
+  <si>
+    <t>Ar ôl sawl munud mae adwaith A wedi gorffen?</t>
+  </si>
+  <si>
+    <t>4.9 munud</t>
+  </si>
+  <si>
+    <t>Beth yw'r enw cemegol ar calchfaen?</t>
+  </si>
+  <si>
+    <t>Calsiwm carbonad</t>
+  </si>
+  <si>
+    <t>Beth yw fformiwla calsiwm carbonad?</t>
+  </si>
+  <si>
+    <t>$CaCO_3$</t>
+  </si>
+  <si>
+    <t>Beth yw'r enw cemegol ar calch brwd?</t>
+  </si>
+  <si>
+    <t>Calsiwm ocsid</t>
+  </si>
+  <si>
+    <t>Beth yw fformiwla calsiwm ocsid?</t>
+  </si>
+  <si>
+    <t>Beth yw'r enw cemegol ar calch tawdd?</t>
+  </si>
+  <si>
+    <t>Calsiwm hydrocsid</t>
+  </si>
+  <si>
+    <t>$Ca(OH)_2$</t>
+  </si>
+  <si>
+    <t>Beth yw DADELFENIAD THERMOL?</t>
+  </si>
+  <si>
+    <t>Pan fydd cyfansoddyn yn cael ei wresogi'n gryf ac yn torri i ffurfio sylweddau llai e.e.&lt;br&gt;&lt;br&gt;calsiwm carbonad    --------&gt;     calsiwm ocsid      +       carbon deuocsid</t>
+  </si>
+  <si>
+    <t>Beth sydd rhai ei wneud i newid calchfaen yn calch brwd?</t>
+  </si>
+  <si>
+    <t>Gwresogi'n gryf</t>
+  </si>
+  <si>
+    <t>Cylchred calchfaen.png</t>
+  </si>
+  <si>
+    <t>Beth sydd rhai ei wneud i newid calch brwd yn calch tawdd?</t>
+  </si>
+  <si>
+    <t>Ychwanegu dŵr - bydd yn hisian a stêm yn ffurfio</t>
+  </si>
+  <si>
+    <t>Beth sydd rhai ei wneud i newid calch tawdd  yn calchfaen?</t>
+  </si>
+  <si>
+    <t>Byrlymu (bubble) carbon deuocsid drwyddo</t>
+  </si>
+  <si>
+    <t>Hafaliad symbol dadelfeniad thermol calchfaen (calsiwm carbonad)</t>
+  </si>
+  <si>
+    <t>$CaCO_3$   -----------&gt;    CaO    +     $CO_2$</t>
+  </si>
+  <si>
+    <t>Hafaliad symbol ychwanegu dŵr i calsiwm ocsid</t>
+  </si>
+  <si>
+    <t>CaO    +      $H_2O$    -----------&gt;    $Ca(OH)_2$</t>
+  </si>
+  <si>
+    <t>sinc carbonad &gt; copr (II) carbonad &gt; plwm carbonad&lt;br&gt;&lt;br&gt;y mwyaf o amser mae'n ei gymryd i ddadelfennu y mwyaf sefydlog yw'r carbonad.</t>
+  </si>
+  <si>
+    <t>Cwestiwn dadelfeniad cymharol.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -888,6 +1058,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -916,7 +1092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -968,6 +1144,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2638,10 +2821,10 @@
   <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="4" width="31.85546875" customWidth="1"/>
+    <col min="1" max="4" width="31.85546875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24.75" customHeight="1">
+    <row r="1" spans="1:9" ht="33.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2660,40 +2843,135 @@
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
     </row>
-    <row r="2" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="3" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="4" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="5" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="6" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="7" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="8" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="9" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="10" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="11" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="12" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="13" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="14" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="15" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="16" spans="1:9" ht="24.75" customHeight="1"/>
-    <row r="17" ht="24.75" customHeight="1"/>
-    <row r="18" ht="24.75" customHeight="1"/>
-    <row r="19" ht="24.75" customHeight="1"/>
-    <row r="20" ht="24.75" customHeight="1"/>
-    <row r="21" ht="24.75" customHeight="1"/>
-    <row r="22" ht="24.75" customHeight="1"/>
-    <row r="23" ht="24.75" customHeight="1"/>
-    <row r="24" ht="24.75" customHeight="1"/>
-    <row r="25" ht="24.75" customHeight="1"/>
-    <row r="26" ht="24.75" customHeight="1"/>
-    <row r="27" ht="24.75" customHeight="1"/>
-    <row r="28" ht="24.75" customHeight="1"/>
-    <row r="29" ht="24.75" customHeight="1"/>
-    <row r="30" ht="24.75" customHeight="1"/>
-    <row r="31" ht="24.75" customHeight="1"/>
-    <row r="32" ht="24.75" customHeight="1"/>
-    <row r="33" ht="24.75" customHeight="1"/>
-    <row r="34" ht="24.75" customHeight="1"/>
-    <row r="35" ht="24.75" customHeight="1"/>
+    <row r="2" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A2" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A3" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A12" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="33.75" customHeight="1"/>
+    <row r="14" spans="1:9" ht="33.75" customHeight="1"/>
+    <row r="15" spans="1:9" ht="33.75" customHeight="1"/>
+    <row r="16" spans="1:9" ht="33.75" customHeight="1"/>
+    <row r="17" ht="33.75" customHeight="1"/>
+    <row r="18" ht="33.75" customHeight="1"/>
+    <row r="19" ht="33.75" customHeight="1"/>
+    <row r="20" ht="33.75" customHeight="1"/>
+    <row r="21" ht="33.75" customHeight="1"/>
+    <row r="22" ht="33.75" customHeight="1"/>
+    <row r="23" ht="33.75" customHeight="1"/>
+    <row r="24" ht="33.75" customHeight="1"/>
+    <row r="25" ht="33.75" customHeight="1"/>
+    <row r="26" ht="33.75" customHeight="1"/>
+    <row r="27" ht="33.75" customHeight="1"/>
+    <row r="28" ht="33.75" customHeight="1"/>
+    <row r="29" ht="33.75" customHeight="1"/>
+    <row r="30" ht="33.75" customHeight="1"/>
+    <row r="31" ht="33.75" customHeight="1"/>
+    <row r="32" ht="33.75" customHeight="1"/>
+    <row r="33" ht="33.75" customHeight="1"/>
+    <row r="34" ht="33.75" customHeight="1"/>
+    <row r="35" ht="33.75" customHeight="1"/>
     <row r="36" ht="24.75" customHeight="1"/>
     <row r="37" ht="24.75" customHeight="1"/>
   </sheetData>
@@ -2703,9 +2981,193 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C18B3CD-C674-494F-83D8-310B8A0DB0B6}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="34.7109375" style="27" customWidth="1"/>
+    <col min="2" max="3" width="34.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A2" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A3" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A12" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A13" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A15" s="10"/>
+    </row>
+    <row r="16" spans="1:4" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A16" s="10"/>
+    </row>
+    <row r="17" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A17" s="10"/>
+    </row>
+    <row r="18" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A18" s="10"/>
+    </row>
+    <row r="19" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A19" s="10"/>
+    </row>
+    <row r="20" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A20" s="10"/>
+    </row>
+    <row r="21" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A21" s="10"/>
+    </row>
+    <row r="22" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A22" s="10"/>
+    </row>
+    <row r="23" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A23" s="10"/>
+    </row>
+    <row r="24" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A24" s="10"/>
+    </row>
+    <row r="25" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A25" s="10"/>
+    </row>
+    <row r="26" spans="1:1" s="9" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A26" s="10"/>
+    </row>
+    <row r="27" spans="1:1" s="9" customFormat="1">
+      <c r="A27" s="10"/>
+    </row>
+    <row r="28" spans="1:1" s="9" customFormat="1">
+      <c r="A28" s="10"/>
+    </row>
+    <row r="29" spans="1:1" s="9" customFormat="1">
+      <c r="A29" s="10"/>
+    </row>
+    <row r="30" spans="1:1" s="9" customFormat="1">
+      <c r="A30" s="10"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/CardiauFflachCemegbl10.xlsx
+++ b/CardiauFflachCemegbl10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1291" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF6CCB99-A144-426B-9416-B7EC4DAEAD7E}"/>
+  <xr:revisionPtr revIDLastSave="1295" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69D729F3-3307-4AF4-93A8-C408ED511111}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1 Y Tabl Cyfnodol ar Atom" sheetId="1" r:id="rId1"/>
@@ -282,16 +282,16 @@
     <t>Atom o'r un elfen sydd gyda'r un nifer o brotonau ac electronau ond nifer GWAHANOL O NIWTRONAU</t>
   </si>
   <si>
-    <t>Rhowch yr CYNHYRCHION sydd yn yr hafaiad yma &lt;br&gt;&lt;br&gt;,br&gt;lithiwm         +          ocsigen     --------&gt;   lithiwm ocsid</t>
-  </si>
-  <si>
-    <t>lithiwm ac ocsigen</t>
+    <t>Rhowch y CYNHYRCHION sydd yn yr hafaiad yma &lt;br&gt;&lt;br&gt;&lt;br&gt;lithiwm         +          ocsigen     --------&gt;   lithiwm ocsid</t>
+  </si>
+  <si>
+    <t>lithiwm ocsid</t>
   </si>
   <si>
     <t>Rhowch yr ADWEITHYDDION sydd yn yr hafaiad yma &lt;br&gt;&lt;br&gt;&lt;br&gt;lithiwm         +          ocsigen     --------&gt;   lithiwm ocsid</t>
   </si>
   <si>
-    <t>lithiwm ocsid</t>
+    <t>lithiwm a ocsigen</t>
   </si>
   <si>
     <t>Beth sy'n cael ei wahanu gyda dull A? &lt;br&gt;Beth yw enw dull A?</t>
@@ -1092,7 +1092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1150,7 +1150,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2985,8 +2984,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="27" customWidth="1"/>
-    <col min="2" max="3" width="34.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+    <col min="2" max="4" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36.75" customHeight="1">
